--- a/examples/example_run_generic_excel/experimental_data/raw_data/2026.06.19_ELISA_plate_raw.xlsx
+++ b/examples/example_run_generic_excel/experimental_data/raw_data/2026.06.19_ELISA_plate_raw.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.2948</t>
+          <t>0.65</t>
         </is>
       </c>
     </row>
